--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104614_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104614_W18.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3209</v>
+        <v>3.0227</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1957</v>
+        <v>1.0681</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1252</v>
+        <v>1.9545</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9411</v>
+        <v>0.9483</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1385</v>
+        <v>-0.1379</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0796</v>
+        <v>1.0862</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1514</v>
+        <v>0.1439</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7896</v>
+        <v>0.8044</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0738</v>
+        <v>-0.3809</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0484</v>
+        <v>-0.1652</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0254</v>
+        <v>-0.2157</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9504</v>
+        <v>2.0426</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0634</v>
+        <v>2.3626</v>
       </c>
       <c r="F3" t="n">
-        <v>0.887</v>
+        <v>-0.32</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2723</v>
+        <v>1.0891</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6566</v>
+        <v>1.1097</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6157</v>
+        <v>-0.0206</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5057</v>
+        <v>0.7857</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1314</v>
+        <v>2.2161</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6371</v>
+        <v>-1.4303</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7665999999999999</v>
+        <v>0.3033</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.788</v>
+        <v>-1.1064</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0214</v>
+        <v>1.4097</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3153</v>
+        <v>0.043</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3157</v>
+        <v>0.4874</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0003</v>
+        <v>-0.4444</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8812</v>
+        <v>2.0074</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0929</v>
+        <v>1.0575</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2117</v>
+        <v>0.9498</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8579</v>
+        <v>-1.2596</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1486</v>
+        <v>-0.6522</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2906</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0172</v>
+        <v>-0.5168</v>
       </c>
       <c r="K4" t="n">
-        <v>0.159</v>
+        <v>0.1239</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8583</v>
+        <v>-0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8752</v>
+        <v>-0.7428</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3075</v>
+        <v>-0.7761</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5676</v>
+        <v>0.0333</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3781</v>
+        <v>0.3564</v>
       </c>
       <c r="T4" t="n">
-        <v>0.983</v>
+        <v>0.3271</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3951</v>
+        <v>0.0294</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7853</v>
+        <v>1.6616</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1644</v>
+        <v>2.5568</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3791</v>
+        <v>-0.8952</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1021</v>
+        <v>-0.8459</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1287</v>
+        <v>-1.1488</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0266</v>
+        <v>0.3029</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8237</v>
+        <v>1.0008</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2472</v>
+        <v>0.1444</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4234</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2784</v>
+        <v>-1.8467</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1185</v>
+        <v>-1.2932</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3968</v>
+        <v>-0.5535</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2241</v>
+        <v>1.1417</v>
       </c>
       <c r="T5" t="n">
-        <v>0.248</v>
+        <v>0.4665</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4721</v>
+        <v>0.6752</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9801</v>
+        <v>0.9301</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9113</v>
+        <v>1.2363</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9312</v>
+        <v>-0.3062</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7749</v>
+        <v>1.5888</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6825</v>
+        <v>0.1006</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0924</v>
+        <v>1.4882</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0938</v>
+        <v>2.6767</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4546</v>
+        <v>0.3308</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6392</v>
+        <v>2.3459</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3189</v>
+        <v>-1.0879</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7721</v>
+        <v>-0.2301</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4532</v>
+        <v>-0.8578</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0711</v>
+        <v>-0.2521</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4053</v>
+        <v>-0.3022</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3342</v>
+        <v>0.0501</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4709</v>
+        <v>0.9091</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0177</v>
+        <v>2.6568</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5468</v>
+        <v>-1.7477</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5899</v>
+        <v>2.7792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1025</v>
+        <v>0.6862</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4874</v>
+        <v>2.0929</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6902</v>
+        <v>3.0786</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3392</v>
+        <v>1.4479</v>
       </c>
       <c r="L7" t="n">
-        <v>2.351</v>
+        <v>1.6308</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1003</v>
+        <v>-0.2995</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2368</v>
+        <v>-0.7617</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8636</v>
+        <v>0.4622</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7068</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5383</v>
+        <v>0.1716</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1685</v>
+        <v>-0.1797</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4914</v>
+        <v>-1.0375</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.249</v>
+        <v>-0.3183</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7575</v>
+        <v>-0.7192</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1026</v>
+        <v>-1.5313</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0173</v>
+        <v>-2.4495</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0853</v>
+        <v>0.9182</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4423</v>
+        <v>-1.419</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4342</v>
+        <v>-1.1419</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0081</v>
+        <v>-0.2771</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6603</v>
+        <v>-0.1124</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5831</v>
+        <v>-1.3077</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0772</v>
+        <v>1.1953</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.162</v>
+        <v>-0.2589</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>0.0112</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3968</v>
+        <v>-0.2702</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8799</v>
+        <v>-1.3686</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1557</v>
+        <v>-2.2101</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7242</v>
+        <v>0.8415</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5047</v>
+        <v>-2.1074</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.4428</v>
+        <v>-2.0163</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9381</v>
+        <v>-0.0911</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3622</v>
+        <v>-1.4644</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1194</v>
+        <v>-1.4414</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2428</v>
+        <v>-0.023</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1425</v>
+        <v>-0.643</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3234</v>
+        <v>-0.5749</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1809</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1218</v>
+        <v>-1.0336</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8861</v>
+        <v>-0.697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2356</v>
+        <v>-0.3366</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8708</v>
+        <v>-2.1253</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6691</v>
+        <v>-3.1705</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7983</v>
+        <v>1.0451</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6688</v>
+        <v>-1.6759</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9811</v>
+        <v>-0.9876</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6877</v>
+        <v>-0.6882</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4035</v>
+        <v>-0.4316</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2931</v>
+        <v>0.2826</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2653</v>
+        <v>-1.2442</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7068</v>
+        <v>0.0545</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9557</v>
+        <v>-0.4138</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2489</v>
+        <v>0.4683</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1202</v>
+        <v>-3.6755</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.438</v>
+        <v>-4.2377</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3178</v>
+        <v>0.5622</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3719</v>
+        <v>-4.3747</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.9103</v>
+        <v>-4.9139</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5384</v>
+        <v>0.5393</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.0052</v>
+        <v>-4.0318</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.7759</v>
+        <v>-3.7931</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3666</v>
+        <v>-0.3428</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0263</v>
+        <v>0.4308</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1966</v>
+        <v>0.4363</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2229</v>
+        <v>-0.0055</v>
       </c>
       <c r="V11" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W11" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.0265</v>
+        <v>2.3666</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9336000000000011</v>
+        <v>1.001499999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>1.092800000000001</v>
+        <v>1.3648</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.370199999999999</v>
+        <v>-5.3894</v>
       </c>
       <c r="H12" t="n">
-        <v>-10.3815</v>
+        <v>-10.4097</v>
       </c>
       <c r="I12" t="n">
-        <v>5.0112</v>
+        <v>5.0204</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05739999999999945</v>
+        <v>-0.1778999999999997</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.580700000000001</v>
+        <v>-2.7208</v>
       </c>
       <c r="L12" t="n">
-        <v>2.6382</v>
+        <v>2.543</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.4277</v>
+        <v>-5.211600000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.8008</v>
+        <v>-7.689</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3732</v>
+        <v>2.4773</v>
       </c>
       <c r="P12" t="n">
-        <v>4.536700000000001</v>
+        <v>4.552699999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2571</v>
+        <v>0.09269999999999995</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.04510000000000003</v>
+        <v>0.3219000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2118</v>
+        <v>-0.2291</v>
       </c>
       <c r="V12" t="n">
-        <v>3.1174</v>
+        <v>3.1107</v>
       </c>
       <c r="W12" t="n">
-        <v>9.994899999999999</v>
+        <v>9.963099999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.8775</v>
+        <v>-6.852399999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4467</v>
+        <v>3.2637</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3319</v>
+        <v>3.5681</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1148</v>
+        <v>-0.3045</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5092</v>
+        <v>5.3948</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3432</v>
+        <v>2.5674</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8339</v>
+        <v>2.8274</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1823</v>
+        <v>5.1595</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7317</v>
+        <v>1.7786</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.914</v>
+        <v>3.3809</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6915</v>
+        <v>0.2352</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6115</v>
+        <v>0.7887</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08</v>
+        <v>-0.5535</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5518</v>
+        <v>-0.6758</v>
       </c>
       <c r="T13" t="n">
-        <v>2.102</v>
+        <v>-0.4046</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5502</v>
+        <v>-0.2713</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1766</v>
+        <v>1.3634</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8983</v>
+        <v>-0.3538</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7217</v>
+        <v>1.7172</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3881</v>
+        <v>0.0765</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5626</v>
+        <v>1.2462</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8255</v>
+        <v>-1.1697</v>
       </c>
       <c r="J14" t="n">
-        <v>5.187</v>
+        <v>-0.2978</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7938</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>3.3931</v>
+        <v>-1.2146</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2011</v>
+        <v>0.3743</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7688</v>
+        <v>0.3294</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5676</v>
+        <v>0.0449</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7578</v>
+        <v>0.1974</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.113</v>
+        <v>-0.0073</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6448</v>
+        <v>0.2047</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1232</v>
+        <v>1.0812</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0288</v>
+        <v>-1.2899</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1521</v>
+        <v>2.3712</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1039</v>
+        <v>1.109</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4211</v>
+        <v>1.4325</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3172</v>
+        <v>-0.3235</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2928</v>
+        <v>0.2713</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4156</v>
+        <v>0.4137</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1228</v>
+        <v>-0.1424</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8111</v>
+        <v>0.8377</v>
       </c>
       <c r="N15" t="n">
-        <v>1.0055</v>
+        <v>1.0189</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2462</v>
+        <v>0.1998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1875</v>
+        <v>-0.4231</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4337</v>
+        <v>0.6229</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2918</v>
+        <v>1.0467</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1505</v>
+        <v>-0.2263</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4423</v>
+        <v>1.2729</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0786</v>
+        <v>0.5145</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2409</v>
+        <v>2.3545</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1622</v>
+        <v>-1.8399</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2743</v>
+        <v>-0.2061</v>
       </c>
       <c r="K16" t="n">
-        <v>0.928</v>
+        <v>1.7237</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2023</v>
+        <v>-1.9298</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3529</v>
+        <v>0.7206</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3129</v>
+        <v>0.6308</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04</v>
+        <v>0.0898</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8794999999999999</v>
+        <v>0.1451</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8347</v>
+        <v>0.5732</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0448</v>
+        <v>-0.4281</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0.387</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0399</v>
+        <v>0.3065</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2992</v>
+        <v>-0.0376</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2593</v>
+        <v>0.3442</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6074</v>
+        <v>-0.5413</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5757</v>
+        <v>0.4538</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1831</v>
+        <v>-0.9951</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0994</v>
+        <v>0.1437</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2224</v>
+        <v>0.3825</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.3218</v>
+        <v>-0.2388</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.508</v>
+        <v>-0.6851</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1387</v>
+        <v>-0.7563</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9402</v>
+        <v>-0.0626</v>
       </c>
       <c r="T17" t="n">
-        <v>1.733</v>
+        <v>-0.1813</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2072</v>
+        <v>0.1187</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0264</v>
+        <v>-0.6294</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2555</v>
+        <v>0.4444</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2291</v>
+        <v>-1.0739</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5412</v>
+        <v>-1.6082</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4531</v>
+        <v>0.5772</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9942</v>
+        <v>-2.1854</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1619</v>
+        <v>-1.1219</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3912</v>
+        <v>1.2098</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2293</v>
+        <v>-2.3317</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.703</v>
+        <v>-0.4863</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0619</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7649</v>
+        <v>0.1463</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3926</v>
+        <v>1.2762</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4174</v>
+        <v>0.9125</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0248</v>
+        <v>0.3637</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5039</v>
+        <v>-1.1658</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4494</v>
+        <v>-2.8243</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9456</v>
+        <v>1.6585</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6251</v>
+        <v>0.6297</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6078</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9191</v>
+        <v>-0.9355</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9564</v>
+        <v>-0.9727</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5442</v>
+        <v>1.5652</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9737</v>
+        <v>0.99</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3247</v>
+        <v>0.6597</v>
       </c>
       <c r="T19" t="n">
-        <v>0.738</v>
+        <v>0.3875</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5867</v>
+        <v>0.2722</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6651</v>
+        <v>-1.2252</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.215</v>
+        <v>-2.7585</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5498</v>
+        <v>1.5333</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0847</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6666</v>
+        <v>0.6718</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7513</v>
+        <v>-1.7565</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.733</v>
+        <v>-1.7456</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6483</v>
+        <v>0.6609</v>
       </c>
       <c r="N20" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3269</v>
+        <v>0.77</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3478</v>
+        <v>0.1253</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6747</v>
+        <v>0.6448</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.723</v>
+        <v>-2.0889</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2295</v>
+        <v>1.5435</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9525</v>
+        <v>-3.6324</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7844</v>
+        <v>1.7846</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8355</v>
+        <v>0.8358</v>
       </c>
       <c r="I21" t="n">
         <v>0.9489</v>
       </c>
       <c r="J21" t="n">
-        <v>3.0096</v>
+        <v>2.984</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9626</v>
+        <v>0.9513</v>
       </c>
       <c r="L21" t="n">
-        <v>2.047</v>
+        <v>2.0327</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2252</v>
+        <v>-1.1993</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1218</v>
+        <v>-0.4866</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.4114</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3566</v>
+        <v>-0.0752</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1863</v>
+        <v>-2.3908</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2474</v>
+        <v>0.5695</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4338</v>
+        <v>-2.9604</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8857</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2657</v>
+        <v>0.2534</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1514</v>
+        <v>-1.139</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9845</v>
+        <v>0.9599</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6992</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8702</v>
+        <v>-1.8455</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9811</v>
+        <v>-0.1881</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2855</v>
+        <v>0.1535</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0265</v>
+        <v>-0.4385999999999992</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.092899999999999</v>
+        <v>-1.364900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9336000000000002</v>
+        <v>0.9261000000000004</v>
       </c>
       <c r="G23" t="n">
-        <v>5.370299999999999</v>
+        <v>5.3893</v>
       </c>
       <c r="H23" t="n">
-        <v>10.3817</v>
+        <v>10.4098</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.0111</v>
+        <v>-5.0204</v>
       </c>
       <c r="J23" t="n">
-        <v>5.427700000000001</v>
+        <v>5.211500000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>7.801</v>
+        <v>7.689</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.373399999999999</v>
+        <v>-2.4775</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.05729999999999968</v>
+        <v>0.1777000000000002</v>
       </c>
       <c r="N23" t="n">
-        <v>2.5806</v>
+        <v>2.7209</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.638</v>
+        <v>-2.543</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.5366</v>
+        <v>-4.5526</v>
       </c>
       <c r="Q23" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R23" t="n">
-        <v>9.073199999999998</v>
+        <v>9.1052</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2569999999999998</v>
+        <v>1.8351</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2117999999999999</v>
+        <v>0.2291000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.04520000000000007</v>
+        <v>1.6059</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.1173</v>
+        <v>-3.1106</v>
       </c>
       <c r="W23" t="n">
-        <v>6.8775</v>
+        <v>6.8524</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.9947</v>
+        <v>-9.963000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104614_W18.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104614_W18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.852399999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104614_W18.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-9.963000000000001</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
